--- a/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N110_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T3269_W0023F0002T0006Z000C1N110_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>51.30343968323768</v>
+        <v>8.336808948526123</v>
       </c>
       <c r="D2" t="n">
-        <v>50.95924088760265</v>
+        <v>8.28087664423543</v>
       </c>
       <c r="E2" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F2" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.49891476529271</v>
+        <v>11.29357364936007</v>
       </c>
       <c r="D3" t="n">
-        <v>69.6246368969141</v>
+        <v>11.31400349574854</v>
       </c>
       <c r="E3" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F3" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>54.3012251874373</v>
+        <v>8.823949092958562</v>
       </c>
       <c r="D4" t="n">
-        <v>39.08312630918932</v>
+        <v>6.351008025243265</v>
       </c>
       <c r="E4" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F4" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>62.84675269079676</v>
+        <v>10.21259731225447</v>
       </c>
       <c r="D5" t="n">
-        <v>31.57926534927626</v>
+        <v>5.131630619257392</v>
       </c>
       <c r="E5" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F5" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>72.13169135888256</v>
+        <v>11.72139984581842</v>
       </c>
       <c r="D6" t="n">
-        <v>21.47673159491453</v>
+        <v>3.489968884173611</v>
       </c>
       <c r="E6" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F6" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>34.56336375530827</v>
+        <v>5.616546610237593</v>
       </c>
       <c r="D7" t="n">
-        <v>35.21291171853138</v>
+        <v>5.722098154261349</v>
       </c>
       <c r="E7" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F7" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>77.80509626182678</v>
+        <v>12.64332814254685</v>
       </c>
       <c r="D8" t="n">
-        <v>6.623045626267939</v>
+        <v>1.07624491426854</v>
       </c>
       <c r="E8" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F8" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>68.63352273609357</v>
+        <v>11.1529474446152</v>
       </c>
       <c r="D9" t="n">
-        <v>15.70031846810758</v>
+        <v>2.551301751067482</v>
       </c>
       <c r="E9" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F9" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>59.99463357900236</v>
+        <v>9.749127956587884</v>
       </c>
       <c r="D10" t="n">
-        <v>8.062257748298549</v>
+        <v>1.310116884098514</v>
       </c>
       <c r="E10" t="n">
-        <v>12.37632960654155</v>
+        <v>2.011153561063002</v>
       </c>
       <c r="F10" t="n">
-        <v>19.49003349505072</v>
+        <v>3.167130442945743</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
